--- a/daily_matches/job_matches_2026-09-06.xlsx
+++ b/daily_matches/job_matches_2026-09-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,350 +468,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Account Solutions Architect - Engaged</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, TensorFlow</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
+          <t>https://www.indeed.com/viewjob?jk=126b2a73151b2dee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist – Predictive Analytics / Predictive ML</t>
+          <t>Account Solutions Architect - Engaged</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bourntec Solutions</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Redshift, BigQuery, MLflow, CI/CD, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, PyTorch, Kubernetes, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b81ed34ffba2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e111636ce8d2904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Remote Sitecore Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mgrm</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, GitHub Actions, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596596549a203384</t>
+          <t>https://www.indeed.com/viewjob?jk=228c20ecd1c04a55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer Databricks</t>
+          <t>Sitecore Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47b109467cc3b863</t>
+          <t>https://www.indeed.com/viewjob?jk=99b3f36d82474b29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Network Reliability Engineer</t>
+          <t>AI expert</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Beautyman Alvstad, LLP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Lake Worth Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a928cddd0171e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56af02a700baff85</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Workflows - Weights &amp; Biases</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Weights &amp; Biases</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, Snowflake, Kafka, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1633bbf9c918e8cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, ML Workflows - Weights &amp; Biases</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Weights &amp; Biases</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Livingston, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, Snowflake, Kafka, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c936937c25c5d00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Engineer - Senior (GCP)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Datafactz</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Northville Tw, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, BigQuery, BigQuery, Tableau, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1114218f82b590c</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Evans Transportation Services</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Delafield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23cf1d12b6b3fb6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1d238a402fe9d76</t>
         </is>
       </c>
     </row>
